--- a/ai4sh/import_data/utility/observation/excel/provision.xlsx
+++ b/ai4sh/import_data/utility/observation/excel/provision.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="125">
   <si>
     <t xml:space="preserve">provider_id__provider_name</t>
   </si>
@@ -37,6 +37,9 @@
     <t xml:space="preserve">alias</t>
   </si>
   <si>
+    <t xml:space="preserve">tag</t>
+  </si>
+  <si>
     <t xml:space="preserve">display_name</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t xml:space="preserve">wetlab</t>
   </si>
   <si>
+    <t xml:space="preserve">ai4sh agrolab</t>
+  </si>
+  <si>
     <t xml:space="preserve">ai4sh-agrolab</t>
   </si>
   <si>
@@ -79,6 +85,9 @@
     <t xml:space="preserve">loennstorp-laboratory-slu</t>
   </si>
   <si>
+    <t xml:space="preserve">ai4sh slu</t>
+  </si>
+  <si>
     <t xml:space="preserve">ai4sh-slu</t>
   </si>
   <si>
@@ -91,6 +100,9 @@
     <t xml:space="preserve">ai4sh-laboratory-veltia</t>
   </si>
   <si>
+    <t xml:space="preserve">ai4sh veltia</t>
+  </si>
+  <si>
     <t xml:space="preserve">ai4sh-veltia</t>
   </si>
   <si>
@@ -103,6 +115,9 @@
     <t xml:space="preserve">ai4sh-laboratory-ibec</t>
   </si>
   <si>
+    <t xml:space="preserve">ai4sh ibec</t>
+  </si>
+  <si>
     <t xml:space="preserve">ai4sh-ibec</t>
   </si>
   <si>
@@ -175,6 +190,9 @@
     <t xml:space="preserve">ai4sh metabarcoding</t>
   </si>
   <si>
+    <t xml:space="preserve">ai4sh-metabarcod</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI4SH metabarcoding</t>
   </si>
   <si>
@@ -193,21 +211,15 @@
     <t xml:space="preserve">digit soil sear bob</t>
   </si>
   <si>
+    <t xml:space="preserve">digit-soil-bob</t>
+  </si>
+  <si>
     <t xml:space="preserve">Digit Soil Enzymatic Activity Reader Bob</t>
   </si>
   <si>
     <t xml:space="preserve">Commercial citizen-science level instrument for analyzing soil enzymatic activity</t>
   </si>
   <si>
-    <t xml:space="preserve">digit soil soil enzymatic activity reader duncan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">digit soil sear duncan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digit Soil Enzymatic Activity Reader Duncan</t>
-  </si>
-  <si>
     <t xml:space="preserve">best infiltration method</t>
   </si>
   <si>
@@ -220,6 +232,9 @@
     <t xml:space="preserve">best infiltration</t>
   </si>
   <si>
+    <t xml:space="preserve">best-infiltration</t>
+  </si>
+  <si>
     <t xml:space="preserve">Beerkan estimation of soil hydraulic properties</t>
   </si>
   <si>
@@ -235,6 +250,9 @@
     <t xml:space="preserve">microbiometer-classic testkit for soil fungi and bacteria</t>
   </si>
   <si>
+    <t xml:space="preserve">ubiometer-classic</t>
+  </si>
+  <si>
     <t xml:space="preserve">Microbiometer classic testkit for soil fungi and bacteria</t>
   </si>
   <si>
@@ -247,6 +265,9 @@
     <t xml:space="preserve">microbiometer-pro testkit for soil fungi and bacteria</t>
   </si>
   <si>
+    <t xml:space="preserve">ubiometer-pro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Microbiometer pro testkit for soil fungi and bacteria</t>
   </si>
   <si>
@@ -277,6 +298,9 @@
     <t xml:space="preserve">aggregate stability wet sieving</t>
   </si>
   <si>
+    <t xml:space="preserve">aggstab-wet-siev</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aggregate stability wet sieving</t>
   </si>
   <si>
@@ -289,6 +313,9 @@
     <t xml:space="preserve">soil cylinder bulk density and volumetric water content</t>
   </si>
   <si>
+    <t xml:space="preserve">soil-cylinder</t>
+  </si>
+  <si>
     <t xml:space="preserve">Volume exact soil cylinder extraction, drying and weighing for determinaton of soil water content (volume*volume^-1) and soil bulk density (mg*ml^-1)</t>
   </si>
   <si>
@@ -316,6 +343,9 @@
     <t xml:space="preserve">foss ds2500 l</t>
   </si>
   <si>
+    <t xml:space="preserve">foss-ds2500-l</t>
+  </si>
+  <si>
     <t xml:space="preserve">FOSS NIRS DS2500 L</t>
   </si>
   <si>
@@ -328,6 +358,9 @@
     <t xml:space="preserve">foss xds rca</t>
   </si>
   <si>
+    <t xml:space="preserve">foss-xds-rca</t>
+  </si>
+  <si>
     <t xml:space="preserve">FOSS XDS RCA</t>
   </si>
   <si>
@@ -340,6 +373,9 @@
     <t xml:space="preserve">bruker invenio s ftir</t>
   </si>
   <si>
+    <t xml:space="preserve">bruker-inv-s-ftir</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bruker Invenio S FTIR</t>
   </si>
   <si>
@@ -350,6 +386,9 @@
   </si>
   <si>
     <t xml:space="preserve">foss micral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foss-micral</t>
   </si>
   <si>
     <t xml:space="preserve">FOSS Micral</t>
@@ -570,7 +609,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.44"/>
@@ -578,8 +617,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="27.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="32.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="27.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="32.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -622,621 +661,661 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="I6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="I7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="J11" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="K11" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>53</v>
+      <c r="A12" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="1" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>62</v>
+      <c r="A13" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H13" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J13" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I14" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J14" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I15" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J15" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I16" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J16" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I17" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I18" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H19" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K20" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>98</v>
+        <v>10</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J21" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K21" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J22" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K22" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>105</v>
+        <v>10</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="J23" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J24" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K23" s="1" t="n">
         <v>1</v>
       </c>
     </row>
